--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC58B70-54B6-4C44-AE25-F4B82A906935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A134B3-47C7-4A39-87D5-5375FB1E5FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="149">
   <si>
     <t>49014</t>
   </si>
@@ -142,9 +142,18 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>5A0ECF768B1442C470761B5187643D28</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>Transferencias, Asignaciones, Subsidios y Otras Ayudas</t>
   </si>
   <si>
@@ -163,277 +172,301 @@
     <t>19/07/2024</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>BDD28C2AEB347E1ACD36528D6312E472</t>
+  </si>
+  <si>
     <t>Aprovechamientos</t>
   </si>
   <si>
+    <t>224187.08</t>
+  </si>
+  <si>
     <t>Ingresos Propios</t>
   </si>
   <si>
     <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
+    <t>5FEBAED1F47BA37C4D67540064E8568F</t>
+  </si>
+  <si>
     <t>Productos</t>
   </si>
   <si>
+    <t>43393.65</t>
+  </si>
+  <si>
+    <t>FF675E5EE834E5CF989B4A9FACA70D97</t>
+  </si>
+  <si>
     <t>Ingresos por Venta de Bienes, Prestación de Servicios y Otros Ingresos</t>
   </si>
   <si>
     <t>Ingresos por ventas de bienes y prestación de servicios</t>
   </si>
   <si>
+    <t>7184954</t>
+  </si>
+  <si>
     <t>Secretaría de Finanzas del Estado de Tlaxcala</t>
   </si>
   <si>
+    <t>20/09/2024</t>
+  </si>
+  <si>
+    <t>3D1BD427874141BDD14EA38E986706E0</t>
+  </si>
+  <si>
     <t>99369</t>
   </si>
   <si>
+    <t>E5CE4FFAAA7FA12DCE04D4247236DA3A</t>
+  </si>
+  <si>
+    <t>146214</t>
+  </si>
+  <si>
+    <t>0D8A8FB9C2A596C6BE3FB55203053867</t>
+  </si>
+  <si>
+    <t>62662</t>
+  </si>
+  <si>
     <t>Recursos Estatales</t>
   </si>
   <si>
+    <t>26/09/2024</t>
+  </si>
+  <si>
+    <t>096FEA55EDC72A2C5755FD212155F88C</t>
+  </si>
+  <si>
     <t>58261</t>
   </si>
   <si>
+    <t>13/09/2024</t>
+  </si>
+  <si>
+    <t>15E902BBE39EF08E8881B1D263179952</t>
+  </si>
+  <si>
+    <t>1741573.5</t>
+  </si>
+  <si>
+    <t>6F6D6A8D6672316318B74BF95DAF82B4</t>
+  </si>
+  <si>
+    <t>6724642</t>
+  </si>
+  <si>
+    <t>85D0685D72F039EAADEB1596C2147DF5</t>
+  </si>
+  <si>
+    <t>1584773.5</t>
+  </si>
+  <si>
+    <t>ACDAA96CA48F1A2187672E4F7510DF99</t>
+  </si>
+  <si>
+    <t>5812785</t>
+  </si>
+  <si>
+    <t>4EE4BCED8CB32B8EFB6B6C1CF5D151F6</t>
+  </si>
+  <si>
+    <t>337956.88</t>
+  </si>
+  <si>
+    <t>553EE45A002833B9C9BF5733032F8616</t>
+  </si>
+  <si>
+    <t>18159347</t>
+  </si>
+  <si>
+    <t>18/09/2024</t>
+  </si>
+  <si>
+    <t>E35DFF9D0E7A10571C88B45E34916D92</t>
+  </si>
+  <si>
+    <t>356911.07</t>
+  </si>
+  <si>
+    <t>31/08/2024</t>
+  </si>
+  <si>
+    <t>413AFCBD46CFBF112BD6034CBBFAFDB4</t>
+  </si>
+  <si>
+    <t>71019.48</t>
+  </si>
+  <si>
+    <t>05805725D6903558ECFA67CBBF2B41A3</t>
+  </si>
+  <si>
+    <t>4962049</t>
+  </si>
+  <si>
+    <t>13/08/2024</t>
+  </si>
+  <si>
+    <t>23DD335DA1C13F5CF463D7A87796A9A5</t>
+  </si>
+  <si>
+    <t>30/08/2024</t>
+  </si>
+  <si>
+    <t>67497BB511FB58A37817DA1774216AC0</t>
+  </si>
+  <si>
     <t>146215</t>
   </si>
   <si>
+    <t>8E7D9D5BBDE4A819786EED8E63254D98</t>
+  </si>
+  <si>
+    <t>60427</t>
+  </si>
+  <si>
+    <t>22/08/2024</t>
+  </si>
+  <si>
+    <t>BFADF1AC9DE5C0D38C42FA5BC574485C</t>
+  </si>
+  <si>
+    <t>98DB69CED8100062472AC26E3A619E28</t>
+  </si>
+  <si>
+    <t>6102842</t>
+  </si>
+  <si>
+    <t>37BC6D6AEF0443D609A97DC1BC1A387E</t>
+  </si>
+  <si>
+    <t>2497717.5</t>
+  </si>
+  <si>
+    <t>1754B320BC6E5D81EBD15D73B9AF2B15</t>
+  </si>
+  <si>
+    <t>5812614</t>
+  </si>
+  <si>
+    <t>309E2395A0048D6ED8E4E80F31BB80DA</t>
+  </si>
+  <si>
+    <t>1128394.5</t>
+  </si>
+  <si>
+    <t>8007EA60CE209CBCA0C297E5E605A8B0</t>
+  </si>
+  <si>
     <t>145439.38</t>
   </si>
   <si>
-    <t>244AE043D7C5299B3EFA9254C03E93F4</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>30/04/2024</t>
-  </si>
-  <si>
-    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Presupuestal.pdf</t>
-  </si>
-  <si>
-    <t>C09599D8EA2558236495689D158E8657</t>
-  </si>
-  <si>
-    <t>731075</t>
-  </si>
-  <si>
-    <t>18/06/2024</t>
-  </si>
-  <si>
-    <t>CF686D39B415C5E24BD1903AEBBB4316</t>
-  </si>
-  <si>
-    <t>624596</t>
-  </si>
-  <si>
-    <t>21/05/2024</t>
-  </si>
-  <si>
-    <t>273479D066074701015922910F1FB5EA</t>
-  </si>
-  <si>
-    <t>07/06/2024</t>
-  </si>
-  <si>
-    <t>BA05C02784A715F36BA4844F29629530</t>
-  </si>
-  <si>
-    <t>19024078</t>
-  </si>
-  <si>
-    <t>12/06/2024</t>
-  </si>
-  <si>
-    <t>6A6DF9948FA1538DCD57F27F1D784C9B</t>
-  </si>
-  <si>
-    <t>153129.42</t>
-  </si>
-  <si>
-    <t>31/05/2024</t>
-  </si>
-  <si>
-    <t>87192A5DC649A5D8371BFBA954DAC302</t>
-  </si>
-  <si>
-    <t>30324.5</t>
-  </si>
-  <si>
-    <t>50DBB6D4A4D91E8A1A2646FA75C3997D</t>
-  </si>
-  <si>
-    <t>126467</t>
-  </si>
-  <si>
-    <t>FBFEA8E9393ACF76F69B698C4F088C7D</t>
-  </si>
-  <si>
-    <t>10104226</t>
-  </si>
-  <si>
-    <t>B81ACD3B8F9362AC75B34774AF74A9BF</t>
-  </si>
-  <si>
-    <t>13338795</t>
-  </si>
-  <si>
-    <t>FBF20376AB81B3A52B3FF30995C5C347</t>
-  </si>
-  <si>
-    <t>148901D7F13E6F3252BEE48785B1E944</t>
-  </si>
-  <si>
-    <t>13/05/2024</t>
-  </si>
-  <si>
-    <t>CA9AB1BD73C53C9A162FD37F96607DF5</t>
-  </si>
-  <si>
-    <t>86795.22</t>
-  </si>
-  <si>
-    <t>22980AA0E8752EB5F739DC80F71B2DB7</t>
-  </si>
-  <si>
-    <t>154526.17</t>
-  </si>
-  <si>
-    <t>B1DD28DD48646AC2E8A6B3688C45B122</t>
-  </si>
-  <si>
-    <t>4156540</t>
-  </si>
-  <si>
-    <t>24/06/2024</t>
-  </si>
-  <si>
-    <t>3DE6F0FC619A8AECC40369FFFA9FC84C</t>
-  </si>
-  <si>
-    <t>42218.95</t>
-  </si>
-  <si>
-    <t>5DB1475BDB839D092A2E9C8652CC7C05</t>
-  </si>
-  <si>
-    <t>193531</t>
-  </si>
-  <si>
-    <t>14/06/2024</t>
-  </si>
-  <si>
-    <t>71BB624021F2286ABED7016A0DF7A577</t>
-  </si>
-  <si>
-    <t>62257</t>
-  </si>
-  <si>
-    <t>96561ABE5F792FD404E217ED5AEFB5C0</t>
-  </si>
-  <si>
-    <t>B7F0C9FB3CA30C1489DA1576F8151B59</t>
-  </si>
-  <si>
-    <t>7563623</t>
-  </si>
-  <si>
-    <t>1E6C25822B361A67371CE11466CBBF1F</t>
-  </si>
-  <si>
-    <t>496845</t>
-  </si>
-  <si>
-    <t>AE00A56A1D8FC7B8F3261F9FF4DD24FB</t>
-  </si>
-  <si>
-    <t>2770236</t>
-  </si>
-  <si>
-    <t>B738C992E8D7CDAA295857A2390C7FAE</t>
-  </si>
-  <si>
-    <t>6880930</t>
-  </si>
-  <si>
-    <t>167D5564BDD31DB1B235DE7CB0A8FE75</t>
-  </si>
-  <si>
-    <t>28/06/2024</t>
-  </si>
-  <si>
-    <t>499C113F6B1C00F03DAE0C3FE7E6E9C9</t>
-  </si>
-  <si>
-    <t>72CA5D0456576E5BEA13C54D16740EBE</t>
-  </si>
-  <si>
-    <t>30580.68</t>
-  </si>
-  <si>
-    <t>0B5F91D010C05ED711758372782522A9</t>
-  </si>
-  <si>
-    <t>7904709</t>
-  </si>
-  <si>
-    <t>19/04/2024</t>
-  </si>
-  <si>
-    <t>F168554DE7379326E67DA16921B8D4A4</t>
-  </si>
-  <si>
-    <t>42610</t>
-  </si>
-  <si>
-    <t>1C86FFD3480419F08184DB7E840E8923</t>
-  </si>
-  <si>
-    <t>72821</t>
-  </si>
-  <si>
-    <t>22/04/2024</t>
-  </si>
-  <si>
-    <t>240A05A27748C9A8B9C28622AD558A70</t>
-  </si>
-  <si>
-    <t>70780</t>
-  </si>
-  <si>
-    <t>15/04/2024</t>
-  </si>
-  <si>
-    <t>F33F32DD4DD099F56DA494CA27CE3483</t>
-  </si>
-  <si>
-    <t>2600962</t>
-  </si>
-  <si>
-    <t>C3B48FE68D211322C3DF5237C3921D43</t>
-  </si>
-  <si>
-    <t>1512232</t>
-  </si>
-  <si>
-    <t>5B74842A147EB323C67955EC7D65CDF4</t>
-  </si>
-  <si>
-    <t>7184545</t>
-  </si>
-  <si>
-    <t>A6947491A933AC2264BB67D33AC723D6</t>
-  </si>
-  <si>
-    <t>12/04/2024</t>
+    <t>EFD1210ADCC1D0868CFC0E795426B2CF</t>
+  </si>
+  <si>
+    <t>18357327</t>
+  </si>
+  <si>
+    <t>26/08/2024</t>
+  </si>
+  <si>
+    <t>492698DBD0338052CA2CDDBE7A4772B8</t>
+  </si>
+  <si>
+    <t>290505.01</t>
+  </si>
+  <si>
+    <t>31/07/2024</t>
+  </si>
+  <si>
+    <t>64CE5617A523A505DF45D53F24142272</t>
+  </si>
+  <si>
+    <t>35045.5</t>
+  </si>
+  <si>
+    <t>32EBEBA199DEB6DC153BBEDB1DE19CAB</t>
+  </si>
+  <si>
+    <t>187495</t>
+  </si>
+  <si>
+    <t>16/07/2024</t>
+  </si>
+  <si>
+    <t>FFB0B8D5B757C2A116992731FFA00F0F</t>
+  </si>
+  <si>
+    <t>8B298578036153A49BC9B89ADCB395CF</t>
+  </si>
+  <si>
+    <t>44B5997318997A01BF8753E9FD2D5744</t>
+  </si>
+  <si>
+    <t>269869</t>
+  </si>
+  <si>
+    <t>29/07/2024</t>
+  </si>
+  <si>
+    <t>F366EB51C388552714F29DACCC548200</t>
+  </si>
+  <si>
+    <t>64536</t>
+  </si>
+  <si>
+    <t>22/07/2024</t>
+  </si>
+  <si>
+    <t>51CD3F40BF752FD433308CE33D3BD432</t>
+  </si>
+  <si>
+    <t>2A1AAEDA981D8714F7952391C5E6534E</t>
+  </si>
+  <si>
+    <t>197980</t>
+  </si>
+  <si>
+    <t>ECA46FB484152ACD926A36883F302E5E</t>
+  </si>
+  <si>
+    <t>3217458</t>
+  </si>
+  <si>
+    <t>392B6568D4E092A4A0D5A6E068D3D6D3</t>
+  </si>
+  <si>
+    <t>11895577.5</t>
+  </si>
+  <si>
+    <t>01A88FC024F495DD5F5148F7F51EEE47</t>
+  </si>
+  <si>
+    <t>2868496</t>
+  </si>
+  <si>
+    <t>BD910A8226C863D5EFDFA29213704D2A</t>
+  </si>
+  <si>
+    <t>10862762.5</t>
+  </si>
+  <si>
+    <t>7248347281A5A13FFCD2C729322FA912</t>
   </si>
 </sst>
 </file>
@@ -839,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
@@ -1038,1234 +1071,1234 @@
     </row>
     <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>57</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="K27" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="H34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="K34" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="K35" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2273,19 +2306,19 @@
         <v>124</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>125</v>
@@ -2294,242 +2327,550 @@
         <v>57</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>57</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L41" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N41" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>48</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
